--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2A8AEE-FE03-4CC3-8014-49C1A59883A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F0CFBE-06BC-43A7-BD6A-1945A13F3396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId7"/>
     <sheet name="DailyMission" sheetId="11" r:id="rId8"/>
     <sheet name="Node" sheetId="10" r:id="rId9"/>
+    <sheet name="InitialTest" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="276">
   <si>
     <t>Index</t>
   </si>
@@ -101,54 +102,27 @@
     <t>A mirracle</t>
   </si>
   <si>
-    <t>f6</t>
-  </si>
-  <si>
     <t>你的文凭</t>
   </si>
   <si>
-    <t>你的大学文凭，全世界最没用的东西\n你学的是什么？</t>
-  </si>
-  <si>
     <t>c5,c6,c7</t>
   </si>
   <si>
-    <t>f7</t>
-  </si>
-  <si>
     <t>你的工作</t>
   </si>
   <si>
-    <t>一份勉强能糊口的编剧工作，为一部庸俗短片攥写剧本。明天下午就要交稿了，你还剩最后半天。</t>
-  </si>
-  <si>
     <t>c8</t>
   </si>
   <si>
-    <t>f8</t>
-  </si>
-  <si>
     <t>哲学学位</t>
   </si>
   <si>
-    <t>f9</t>
-  </si>
-  <si>
     <t>比较文学学位</t>
   </si>
   <si>
-    <t>f10</t>
-  </si>
-  <si>
     <t>社会学学位</t>
   </si>
   <si>
-    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。\n\n显然这对找到一份工作没有什么帮助。</t>
-  </si>
-  <si>
-    <t>f11</t>
-  </si>
-  <si>
     <t>烦躁</t>
   </si>
   <si>
@@ -173,111 +147,51 @@
     <t>？！？</t>
   </si>
   <si>
-    <t>f14</t>
-  </si>
-  <si>
     <t>沙漠</t>
   </si>
   <si>
     <t>Nature</t>
   </si>
   <si>
-    <t>f15</t>
-  </si>
-  <si>
     <t>战争</t>
   </si>
   <si>
     <t>Politics</t>
   </si>
   <si>
-    <t>f16</t>
-  </si>
-  <si>
     <t>冻土</t>
   </si>
   <si>
     <t>那些冰冷而坚硬的泥土总是让你想到冻得太过的冰激凌。</t>
   </si>
   <si>
-    <t>f17</t>
-  </si>
-  <si>
     <t>罪</t>
   </si>
   <si>
     <t>10岁的时候你找到了妈妈藏在衣柜里的1万块钱。100张颜色鲜艳的纸片，每次想吃麦当劳了你就会偷偷去拿出来几张。\n一个暑假过去，你也不知道你到底偷拿了多少张。不过你清晰地记得妈妈发现时看着你的眼神。</t>
   </si>
   <si>
-    <t>f18</t>
-  </si>
-  <si>
-    <t>你的工作!</t>
-  </si>
-  <si>
-    <t>你写不出来</t>
-  </si>
-  <si>
     <t>c9</t>
   </si>
   <si>
-    <t>f19</t>
-  </si>
-  <si>
-    <t>你的工作!!</t>
-  </si>
-  <si>
     <t>c10</t>
   </si>
   <si>
-    <t>f20</t>
-  </si>
-  <si>
-    <t>你的工作!!!</t>
-  </si>
-  <si>
-    <t>c11,c12</t>
-  </si>
-  <si>
-    <t>f21</t>
-  </si>
-  <si>
-    <t>是的，你写不出来了，你不得不承认这个事实。</t>
-  </si>
-  <si>
-    <t>c13,c14,c15</t>
-  </si>
-  <si>
-    <t>f22</t>
-  </si>
-  <si>
     <t>酒</t>
   </si>
   <si>
     <t>c16</t>
   </si>
   <si>
-    <t>f23</t>
-  </si>
-  <si>
     <t>遗忘</t>
   </si>
   <si>
-    <t>f24</t>
-  </si>
-  <si>
     <t>痛苦</t>
   </si>
   <si>
-    <t>f25</t>
-  </si>
-  <si>
     <t>幸福</t>
   </si>
   <si>
-    <t>f26</t>
-  </si>
-  <si>
     <t>ChoiceText</t>
   </si>
   <si>
@@ -353,66 +267,30 @@
     <t>比较文学</t>
   </si>
   <si>
-    <t>f14,f15,f9</t>
-  </si>
-  <si>
     <t>c7</t>
   </si>
   <si>
     <t>社会学</t>
   </si>
   <si>
-    <t>f16,f17,f10</t>
-  </si>
-  <si>
-    <t>开始干活</t>
-  </si>
-  <si>
-    <t>干活</t>
-  </si>
-  <si>
-    <t>干活！！</t>
-  </si>
-  <si>
     <t>c11</t>
   </si>
   <si>
-    <t>去喝一杯吧</t>
-  </si>
-  <si>
     <t>c12</t>
   </si>
   <si>
-    <t>干活！！！</t>
-  </si>
-  <si>
-    <t>不，你意识到你今晚肯定是写不出来了</t>
-  </si>
-  <si>
     <t>c13</t>
   </si>
   <si>
-    <t>我写了多少了？</t>
-  </si>
-  <si>
-    <t>只有一个大纲，内容基本没有。简单来说：你完了</t>
-  </si>
-  <si>
     <t>c14</t>
   </si>
   <si>
     <t>c15</t>
   </si>
   <si>
-    <t>还有一个上午，我早上能写的出来的。</t>
-  </si>
-  <si>
     <t>喝</t>
   </si>
   <si>
-    <t>f23,f23,f24,f25</t>
-  </si>
-  <si>
     <t>Forge_Index</t>
   </si>
   <si>
@@ -551,36 +429,15 @@
     <t>m21</t>
   </si>
   <si>
-    <t>c8,c13</t>
-  </si>
-  <si>
-    <t>世界上唯一的万能药 \n 消耗：意志力+3</t>
-  </si>
-  <si>
-    <t>我们必须想象西西弗斯是幸福的 \n 消耗：意志力-2</t>
-  </si>
-  <si>
     <t>闲言</t>
   </si>
   <si>
-    <t>世界局势，蔬菜价格，失业，指甲颜色，新电影，婚外情。\n\n 你可以试着将它压缩成灵感,但请不要抱有太多期待</t>
-  </si>
-  <si>
     <t>c17</t>
   </si>
   <si>
     <t>m1</t>
   </si>
   <si>
-    <t>我完了。</t>
-  </si>
-  <si>
-    <t>不管写了多少，你明天下午三点前一点得去一趟那个胖子的办公室，如果你还想要这份工作的话。\n\n从这儿过去得两个小时，你最好早点出门。</t>
-  </si>
-  <si>
-    <t>好吧，祝你好运，明天下午三点交稿。那之前你得到那个胖子的办公室。\n\n从这儿过去得两个小时，你最好早点出门。</t>
-  </si>
-  <si>
     <t>压缩</t>
   </si>
   <si>
@@ -599,201 +456,524 @@
     <t>Underground_Book</t>
   </si>
   <si>
-    <t>\n\n每天不能喝太多。</t>
-  </si>
-  <si>
-    <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。 \n 消耗：意志力+5</t>
-  </si>
-  <si>
-    <t>f27</t>
-  </si>
-  <si>
     <t>烟</t>
   </si>
   <si>
-    <t>可以让你清醒一点，但对身体不太好。\n\n每天不能抽太多。</t>
-  </si>
-  <si>
     <t>c18</t>
   </si>
   <si>
-    <t>f28</t>
-  </si>
-  <si>
     <t>维他柠檬茶</t>
   </si>
   <si>
-    <t>上学的时候，你最幸福的事情就是翻墙到学校后面的超市买柠檬茶喝。\n\n对于成年人来说有些太甜了。</t>
-  </si>
-  <si>
     <t>c19</t>
   </si>
   <si>
+    <t>灰</t>
+  </si>
+  <si>
+    <t>抽烟</t>
+  </si>
+  <si>
+    <t>CanBeDropped</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dm1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoneyReward</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredCards</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f30</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f13</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>f30</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raw</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>c20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCard</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩证法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>谜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>灰</t>
-  </si>
-  <si>
-    <t>f31</t>
-  </si>
-  <si>
-    <t>抽烟</t>
-  </si>
-  <si>
-    <t>f29,f30</t>
-  </si>
-  <si>
-    <t>正题：你能用它来解决任何问题。 
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛苦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dm2</t>
+  </si>
+  <si>
+    <t>dm3</t>
+  </si>
+  <si>
+    <t>dm4</t>
+  </si>
+  <si>
+    <t>理性灰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻土沙漠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩证法理性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理性沙漠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f14,f16</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f14</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f12</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器，熵</t>
+  </si>
+  <si>
+    <t>机器，帝国</t>
+  </si>
+  <si>
+    <t>机器，疯狂</t>
+  </si>
+  <si>
+    <t>革命，冬</t>
+  </si>
+  <si>
+    <t>革命，帝国</t>
+  </si>
+  <si>
+    <t>复仇，辩证法</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>复仇，律法</t>
+  </si>
+  <si>
+    <t>律法，奇迹</t>
+  </si>
+  <si>
+    <t>债，奇迹</t>
+  </si>
+  <si>
+    <t>丛林</t>
+  </si>
+  <si>
+    <t>平原</t>
+  </si>
+  <si>
+    <t>荒原</t>
+  </si>
+  <si>
+    <t>熵，谜</t>
+  </si>
+  <si>
+    <t>谜，幻觉</t>
+  </si>
+  <si>
+    <t>公元前7000</t>
+  </si>
+  <si>
+    <t>群岛</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>沼泽</t>
+  </si>
+  <si>
+    <t>遥远</t>
+  </si>
+  <si>
+    <t>周围</t>
+  </si>
+  <si>
+    <t>内部</t>
+  </si>
+  <si>
+    <t>热带</t>
+  </si>
+  <si>
+    <t>温带</t>
+  </si>
+  <si>
+    <t>寒带</t>
+  </si>
+  <si>
+    <t>Hui</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LiXing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cigarette</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>XingFu</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TongKu</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>YiWang</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zui</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DongTu</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZhanZheng</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShaMo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mi</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BianZhengFa</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FanZao</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Literature</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Philosophy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sociology</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Work</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diploma</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alcohol</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icetea</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>YiWang,YiWang,TongKu,XingFu</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BianZhengFa,Mi,Philosophy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DongTu,Zui,Literature</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShaMo,ZhanZheng,Sociology</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LiXing,Hui</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
+显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。
+显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。
+显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>正题：你能用它来解决任何问题。
 反题：解决完之后那些问题会变得没用。
 合题：但是你能用它来解决任何问题</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你写不出来，缪斯今晚显然并不眷顾你。
-可能也不止今晚。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。
-显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
-显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CanBeDropped</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Index</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>dm1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoneyReward</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequiredCards</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f30</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f12</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f13</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f30</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>test</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raw</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>c20</t>
-  </si>
-  <si>
-    <t>c20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>testCard</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>辩证法</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f12,f13,f29,f30,f31</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>谜</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>理性</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>灰</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>痛苦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f12,f13,f8,f31</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>dm2</t>
-  </si>
-  <si>
-    <t>dm3</t>
-  </si>
-  <si>
-    <t>dm4</t>
-  </si>
-  <si>
-    <t>理性灰</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>冻土沙漠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>辩证法理性</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>理性沙漠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f14,f16</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f14</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f12</t>
+  </si>
+  <si>
+    <t>每天不能喝太多。</t>
+  </si>
+  <si>
+    <t>世界局势，蔬菜价格，失业，指甲颜色，新电影，婚外情。
+你可以试着将它压缩成灵感,但请不要抱有太多期待</t>
+  </si>
+  <si>
+    <t>可以让你清醒一点，但对身体不太好。
+每天不能抽太多。</t>
+  </si>
+  <si>
+    <t>上学的时候，你最幸福的事情就是翻墙到学校后面的超市买柠檬茶喝。
+对于成年人来说有些太甜了。</t>
+  </si>
+  <si>
+    <t>你的大学文凭，全世界最没用的东西
+你学的是什么？</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hai</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PingYuan</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shan</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>QunDao</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CongLin</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HuangYuan</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZhaoZe</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻觉</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>复仇</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>熵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>律法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>债</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝国</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>革命</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>疯狂</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HuanJue</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhai</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FengKuang</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FuChou</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>QiJi</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiGuo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shang</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LvFa</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GeMing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>JiQi</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡在水里</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小雨</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>干旱</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>火</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>谜，火</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界上唯一的万能药。
+意志力+3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们必须想象西西弗斯是幸福的。
+意志力-2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。
+意志力+5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>为短片攥写剧本,  一份勉强能糊口的编剧工作，自然也谈不上什么文学追求。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardHint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredCard</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>c8,c9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +981,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,13 +1037,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -886,8 +1059,38 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="DengXian"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="DengXian"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -930,6 +1133,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -978,7 +1187,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1018,34 +1227,104 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1054,6 +1333,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7C80"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1260,73 +1544,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="4" max="4" width="37.125" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="7.75" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="11.875" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="I1" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="11" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -1336,7 +1624,7 @@
       <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="22" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="11">
@@ -1349,7 +1637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="11" t="s">
         <v>17</v>
       </c>
@@ -1359,7 +1647,7 @@
       <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="22" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="11">
@@ -1372,563 +1660,495 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I5" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="42.75">
+      <c r="A6" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C6" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="I6" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="D7" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="I7" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C9" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D9" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="I6" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="C10" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D10" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="1:10" s="45" customFormat="1">
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="36">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16.5">
+      <c r="A16" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A17" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="36">
+        <v>3</v>
+      </c>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A18" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="B18" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="36">
+        <v>-2</v>
+      </c>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="57">
+      <c r="A19" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="E19" s="36">
+        <v>5</v>
+      </c>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="I22" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="D24" s="22"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="11">
-        <v>-1</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I17" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="11">
-        <v>3</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="11">
-        <v>-2</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="11">
-        <v>5</v>
-      </c>
-      <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>173</v>
+    <row r="25" spans="1:9">
+      <c r="A25" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>175</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
       <c r="I25" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>189</v>
+    <row r="26" spans="1:9">
+      <c r="A26" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>192</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>191</v>
+        <v>30</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="I26" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>193</v>
+    <row r="27" spans="1:9">
+      <c r="A27" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>186</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>195</v>
+        <v>30</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="I27" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
-        <v>212</v>
+    <row r="28" spans="1:9">
+      <c r="A28" s="17" t="s">
+        <v>207</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="12"/>
       <c r="F28" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
@@ -1936,105 +2156,385 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>197</v>
+    <row r="29" spans="1:9">
+      <c r="A29" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>191</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
+        <v>30</v>
+      </c>
       <c r="F29" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+        <v>36</v>
+      </c>
       <c r="I29" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>220</v>
+    <row r="30" spans="1:9">
+      <c r="A30" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="I30" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+    <row r="31" spans="1:9">
+      <c r="A31" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="22"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+      <c r="I34" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="16.5">
+      <c r="A35" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="16.5">
+      <c r="A36" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="16.5">
+      <c r="A39" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="16.5">
+      <c r="A40" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="16.5">
+      <c r="A41" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="16.5">
+      <c r="A42" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16.5">
+      <c r="A43" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="16.5">
+      <c r="A44" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="16.5">
+      <c r="A45" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I45" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="22"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2043,10 +2543,161 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3408FBE-15D1-42A9-9BFC-EC3E7DE1593E}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5">
+      <c r="A2" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20">
+        <v>0</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20">
+        <v>1871</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20">
+        <v>3027</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T26"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="19.625" customWidth="1"/>
@@ -2061,53 +2712,53 @@
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B1" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="11" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11" t="b">
@@ -2121,15 +2772,15 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>13</v>
@@ -2148,15 +2799,15 @@
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -2171,12 +2822,12 @@
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="11" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -2192,16 +2843,16 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="11" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="21" t="s">
-        <v>228</v>
+      <c r="D6" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2215,16 +2866,16 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="11" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
-        <v>104</v>
+      <c r="D7" s="17" t="s">
+        <v>222</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2238,16 +2889,16 @@
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="11" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
-        <v>107</v>
+      <c r="D8" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2261,196 +2912,128 @@
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>108</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B9" s="12"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="D9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B10" s="12"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="D10" s="12"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>110</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B11" s="12"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="D11" s="12"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>112</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B12" s="12"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="D12" s="12"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>115</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
-      <c r="F13" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="b">
-        <v>0</v>
-      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>118</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
-      <c r="F14" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="b">
-        <v>0</v>
-      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="11"/>
-      <c r="K14" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>178</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11" t="b">
-        <v>0</v>
-      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>179</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
-      <c r="F16" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11" t="b">
-        <v>0</v>
-      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20">
       <c r="A17" s="11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2461,8 +3044,8 @@
       <c r="G17" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>123</v>
+      <c r="H17" s="18" t="s">
+        <v>220</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -2470,12 +3053,12 @@
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20">
       <c r="A18" s="12" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2486,21 +3069,21 @@
       <c r="G18" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="H18" s="15"/>
+      <c r="H18" s="14"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20">
       <c r="A19" s="11" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="11" t="s">
-        <v>200</v>
+      <c r="D19" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -2509,7 +3092,7 @@
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="15"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
@@ -2523,16 +3106,16 @@
       <c r="S19" s="12"/>
       <c r="T19" s="12"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20">
       <c r="A20" s="11" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="11" t="s">
-        <v>76</v>
+      <c r="D20" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="b">
@@ -2555,31 +3138,21 @@
       <c r="S20" s="12"/>
       <c r="T20" s="12"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>217</v>
-      </c>
+    <row r="21" spans="1:20">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="22" t="s">
-        <v>223</v>
-      </c>
+      <c r="D21" s="12"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+    <row r="22" spans="1:20">
+      <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2591,8 +3164,8 @@
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
+    <row r="23" spans="1:20">
+      <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -2604,7 +3177,7 @@
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2617,7 +3190,7 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2630,7 +3203,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2643,19 +3216,6 @@
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2664,30 +3224,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BEFD67-833C-4C4B-AEEA-212EA8D4541D}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>84</v>
+      <c r="B1" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2699,43 +3263,43 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="B1" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -2750,24 +3314,24 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="8"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="F3" s="11" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="6"/>
@@ -2782,24 +3346,24 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>227</v>
+        <v>159</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -2814,24 +3378,24 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>213</v>
+    <row r="5" spans="1:18">
+      <c r="A5" s="16" t="s">
+        <v>151</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -2846,24 +3410,24 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
-        <v>216</v>
+    <row r="6" spans="1:18">
+      <c r="A6" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>227</v>
+        <v>39</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>226</v>
+        <v>162</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -2878,7 +3442,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="B7" s="6"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2897,7 +3461,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="B8" s="6"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2916,7 +3480,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="B9" s="6"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2935,7 +3499,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="6"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="B10" s="6"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2954,7 +3518,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="6"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="B11" s="6"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2973,7 +3537,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="6"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -2992,7 +3556,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="B13" s="6"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -3011,7 +3575,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="6"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="B14" s="6"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -3030,7 +3594,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="B15" s="6"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -3049,7 +3613,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="6"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="B16" s="6"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -3068,7 +3632,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18">
       <c r="B17" s="7"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -3087,7 +3651,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18">
       <c r="B18" s="8"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -3115,17 +3679,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3140,79 +3704,79 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="B3" s="6"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="B6" s="6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="B11" s="6"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="B16" s="6"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2">
       <c r="B17" s="7"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2">
       <c r="B18" s="8"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2">
       <c r="B21" s="10"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2">
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2">
       <c r="B23" s="10"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2">
       <c r="B24" s="10"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2">
       <c r="B25" s="10"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:2">
       <c r="B26" s="10"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:2">
       <c r="B27" s="10"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:2">
       <c r="B28" s="10"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:2">
       <c r="B29" s="10"/>
     </row>
   </sheetData>
@@ -3224,43 +3788,43 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3272,43 +3836,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3320,81 +3884,81 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF9A1A-285A-4BA7-8832-B2D0F52F1F9B}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.125" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>232</v>
+    <row r="1" spans="1:4">
+      <c r="A1" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>167</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>233</v>
+      <c r="D2" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>168</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>234</v>
+      <c r="D3" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>169</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>235</v>
+      <c r="D4" s="16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>170</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>237</v>
+      <c r="D5" s="16" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3406,185 +3970,185 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="11" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="11" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="11" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="11" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="11" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="11" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F0CFBE-06BC-43A7-BD6A-1945A13F3396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A649A8-15A0-41AD-8BD4-3FB166A943FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="275">
   <si>
     <t>Index</t>
   </si>
@@ -333,9 +333,6 @@
     <t>Club</t>
   </si>
   <si>
-    <t>Downtown</t>
-  </si>
-  <si>
     <t>EdditorOffice</t>
   </si>
   <si>
@@ -345,9 +342,6 @@
     <t>Home</t>
   </si>
   <si>
-    <t>Home_Street</t>
-  </si>
-  <si>
     <t>McDonalds</t>
   </si>
   <si>
@@ -363,12 +357,6 @@
     <t>Sea</t>
   </si>
   <si>
-    <t>Street_Book</t>
-  </si>
-  <si>
-    <t>Street_NewDistrict</t>
-  </si>
-  <si>
     <t>Supermarket</t>
   </si>
   <si>
@@ -518,22 +506,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>test</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raw</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>c20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>testCard</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>辩证法</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -670,10 +642,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Test</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>LiXing</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -751,18 +719,6 @@
   </si>
   <si>
     <t>YiWang,YiWang,TongKu,XingFu</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BianZhengFa,Mi,Philosophy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DongTu,Zui,Literature</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShaMo,ZhanZheng,Sociology</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -965,15 +921,57 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>CardHint</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>RequiredCard</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>c8,c9</t>
+    <t>NewDistrict</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oak Rd</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Downtown</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WestHill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guang</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RefreshChoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaximumUse</t>
+  </si>
+  <si>
+    <t>BianZhengFa,Mi</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DongTu,Zui</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShaMo,ZhanZheng</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recall what you have learned</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -981,7 +979,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1071,6 +1069,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="DengXian"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1088,6 +1087,12 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1187,7 +1192,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1249,16 +1254,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1270,25 +1269,19 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1300,7 +1293,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1312,19 +1305,10 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1544,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1554,10 +1538,11 @@
     <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="11.875" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1">
+    <row r="1" spans="1:14" s="2" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1583,38 +1568,41 @@
         <v>7</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="27" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="I2" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1612,7 @@
       <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="11">
@@ -1637,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:14">
       <c r="A4" s="11" t="s">
         <v>17</v>
       </c>
@@ -1647,7 +1635,7 @@
       <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="11">
@@ -1660,451 +1648,489 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="I5" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="42.75">
-      <c r="A6" s="26" t="s">
+    <row r="5" spans="1:14" ht="42.75">
+      <c r="A5" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="D11" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="I7" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="D12" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:10" s="45" customFormat="1">
-      <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="36" t="s">
+      <c r="D13" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C14" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="36">
+      <c r="D14" s="37"/>
+      <c r="E14" s="32">
         <v>-1</v>
       </c>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.5">
+      <c r="A15" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
       <c r="H15" s="36"/>
-      <c r="I15" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16.5">
-      <c r="A16" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="36" t="s">
+      <c r="I15" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="36" t="b">
+      <c r="D16" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E16" s="32">
+        <v>3</v>
+      </c>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A17" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="36" t="s">
+      <c r="A17" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="36">
-        <v>3</v>
-      </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A18" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="36" t="s">
+      <c r="D17" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="32">
+        <v>-2</v>
+      </c>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="57">
+      <c r="A18" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="E18" s="36">
-        <v>-2</v>
-      </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="57">
-      <c r="A19" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="E19" s="36">
+      <c r="D18" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="32">
         <v>5</v>
       </c>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36" t="b">
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" s="27" t="b">
+      <c r="A20" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="27" t="b">
+      <c r="A21" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="27" t="b">
+      <c r="A22" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="I23" s="27" t="b">
+      <c r="A23" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>84</v>
+      <c r="A24" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>183</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="11"/>
       <c r="F24" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
+        <v>36</v>
+      </c>
       <c r="I24" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>142</v>
+      <c r="A25" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>177</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="11"/>
       <c r="F25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+        <v>36</v>
+      </c>
       <c r="I25" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="16" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>30</v>
@@ -2118,10 +2144,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="16" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>30</v>
@@ -2134,154 +2160,145 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>39</v>
+      <c r="A28" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>176</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="12"/>
       <c r="F28" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
       <c r="I28" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>191</v>
+      <c r="A29" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="12"/>
       <c r="F29" s="11" t="s">
         <v>36</v>
       </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
       <c r="I29" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" ht="16.5">
       <c r="A30" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>185</v>
+        <v>240</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>229</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I30" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>180</v>
+    <row r="31" spans="1:9" ht="16.5">
+      <c r="A31" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>234</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I31" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>190</v>
+      <c r="A32" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D32" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="12"/>
       <c r="F32" s="11" t="s">
-        <v>36</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
       <c r="I32" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>35</v>
+      <c r="A33" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="16.5">
+      <c r="A34" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>230</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="12"/>
       <c r="F34" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
+        <v>38</v>
+      </c>
       <c r="I34" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5">
-      <c r="A35" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>241</v>
+      <c r="A35" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="I35" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5">
-      <c r="A36" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="B36" s="25" t="s">
+      <c r="A36" s="16" t="s">
         <v>246</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>235</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>30</v>
@@ -2293,35 +2310,46 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>29</v>
+    <row r="37" spans="1:9" ht="16.5">
+      <c r="A37" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>231</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="E37" s="12"/>
       <c r="F37" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
       <c r="I37" s="11" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="38" spans="1:9" ht="16.5">
+      <c r="A38" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="39" spans="1:9" ht="16.5">
-      <c r="A39" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>242</v>
+      <c r="A39" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>237</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>30</v>
@@ -2334,205 +2362,120 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.5">
-      <c r="A40" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>245</v>
+      <c r="A40" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>238</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I40" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16.5">
-      <c r="A41" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>247</v>
+    <row r="41" spans="1:9">
+      <c r="A41" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" t="s">
+        <v>236</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I41" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="16.5">
-      <c r="A42" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>243</v>
+    <row r="42" spans="1:9">
+      <c r="A42" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D42" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="12"/>
       <c r="F42" s="11" t="s">
         <v>31</v>
       </c>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
       <c r="I42" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="16.5">
-      <c r="A43" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>244</v>
+    <row r="43" spans="1:9">
+      <c r="A43" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D43" s="21"/>
+      <c r="E43" s="12"/>
       <c r="F43" s="11" t="s">
         <v>38</v>
       </c>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
       <c r="I43" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="16.5">
-      <c r="A44" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>249</v>
+    <row r="44" spans="1:9">
+      <c r="A44" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>254</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>30</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I44" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="16.5">
-      <c r="A45" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>250</v>
+    <row r="45" spans="1:9">
+      <c r="A45" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D45" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="12"/>
       <c r="F45" s="11" t="s">
-        <v>38</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
       <c r="I45" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="B46" t="s">
-        <v>248</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="22"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2551,67 +2494,67 @@
     <row r="1" spans="1:10">
       <c r="A1" s="20"/>
       <c r="B1" s="20" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
       <c r="G1" s="20"/>
       <c r="H1" s="20" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5">
       <c r="A2" s="20" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E2" s="19"/>
       <c r="F2" s="19"/>
       <c r="G2" s="20" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>268</v>
+        <v>180</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>256</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="20" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
@@ -2619,24 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="20" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>35</v>
@@ -2647,13 +2590,13 @@
         <v>1871</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2667,13 +2610,13 @@
         <v>3027</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2852,7 +2795,7 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="17" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2875,7 +2818,7 @@
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="17" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2898,7 +2841,7 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="17" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2916,13 +2859,22 @@
       <c r="A9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="18" t="s">
+        <v>274</v>
+      </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="F9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
     </row>
@@ -2930,13 +2882,22 @@
       <c r="A10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="18" t="s">
+        <v>274</v>
+      </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="F10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
     </row>
@@ -2944,13 +2905,22 @@
       <c r="A11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="18" t="s">
+        <v>274</v>
+      </c>
       <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="F11" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
@@ -3045,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -3055,10 +3025,10 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3076,14 +3046,14 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>143</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="17" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -3092,7 +3062,7 @@
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="21"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
@@ -3108,14 +3078,14 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>82</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="17" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="b">
@@ -3239,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>51</v>
@@ -3270,16 +3240,16 @@
         <v>83</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3299,7 +3269,7 @@
         <v>84</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -3322,7 +3292,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>35</v>
@@ -3357,13 +3327,13 @@
         <v>35</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -3380,7 +3350,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="16" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>84</v>
@@ -3389,10 +3359,10 @@
         <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>27</v>
@@ -3412,22 +3382,22 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3893,72 +3863,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>145</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -3985,31 +3955,31 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>101</v>
+        <v>127</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>93</v>
@@ -4017,39 +3987,39 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>97</v>
+        <v>111</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>96</v>
@@ -4057,7 +4027,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>95</v>
@@ -4065,47 +4035,47 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>94</v>
@@ -4113,42 +4083,42 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A649A8-15A0-41AD-8BD4-3FB166A943FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305D32EE-2FEF-4594-8BA7-4D35B119F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
     <sheet name="Raw_Choice" sheetId="5" r:id="rId2"/>
-    <sheet name="EventCard_Choices" sheetId="12" r:id="rId3"/>
-    <sheet name="ForgeLibrary_Universal" sheetId="6" r:id="rId4"/>
-    <sheet name="ForgeLibrary_Nature" sheetId="8" r:id="rId5"/>
-    <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId6"/>
-    <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId7"/>
-    <sheet name="DailyMission" sheetId="11" r:id="rId8"/>
-    <sheet name="Node" sheetId="10" r:id="rId9"/>
-    <sheet name="InitialTest" sheetId="13" r:id="rId10"/>
+    <sheet name="Character" sheetId="13" r:id="rId3"/>
+    <sheet name="CharacterChoices" sheetId="14" r:id="rId4"/>
+    <sheet name="ForgeLibrary_Universal" sheetId="6" r:id="rId5"/>
+    <sheet name="ForgeLibrary_Nature" sheetId="8" r:id="rId6"/>
+    <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId7"/>
+    <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId8"/>
+    <sheet name="DailyMission" sheetId="11" r:id="rId9"/>
+    <sheet name="Node" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="278">
   <si>
     <t>Index</t>
   </si>
@@ -66,42 +66,18 @@
     <t>Choices</t>
   </si>
   <si>
-    <t>f1</t>
-  </si>
-  <si>
-    <t>EmotionCreatorTest</t>
-  </si>
-  <si>
     <t>Raw</t>
   </si>
   <si>
-    <t>Raw Card Test</t>
-  </si>
-  <si>
-    <t>c1,c2,c3,c4</t>
-  </si>
-  <si>
     <t>f2</t>
   </si>
   <si>
-    <t>PainTest</t>
-  </si>
-  <si>
     <t>Emotion</t>
   </si>
   <si>
-    <t>Eternal</t>
-  </si>
-  <si>
     <t>f3</t>
   </si>
   <si>
-    <t>HapinessTest</t>
-  </si>
-  <si>
-    <t>A mirracle</t>
-  </si>
-  <si>
     <t>你的文凭</t>
   </si>
   <si>
@@ -330,12 +306,6 @@
     <t>Cinema</t>
   </si>
   <si>
-    <t>Club</t>
-  </si>
-  <si>
-    <t>EdditorOffice</t>
-  </si>
-  <si>
     <t>Gallery</t>
   </si>
   <si>
@@ -463,67 +433,63 @@
   </si>
   <si>
     <t>CanBeDropped</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Index</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>dm1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MoneyReward</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RequiredCards</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f30</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>f29</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>f12</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>f13</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>f30</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>辩证法</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>谜</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>理性</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>灰</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>痛苦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>dm2</t>
@@ -536,63 +502,24 @@
   </si>
   <si>
     <t>理性灰</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>冻土沙漠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>辩证法理性</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>理性沙漠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f14,f16</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f14</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29,f12</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>机器，熵</t>
-  </si>
-  <si>
-    <t>机器，帝国</t>
-  </si>
-  <si>
-    <t>机器，疯狂</t>
-  </si>
-  <si>
-    <t>革命，冬</t>
-  </si>
-  <si>
-    <t>革命，帝国</t>
-  </si>
-  <si>
-    <t>复仇，辩证法</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>山</t>
   </si>
   <si>
-    <t>复仇，律法</t>
-  </si>
-  <si>
-    <t>律法，奇迹</t>
-  </si>
-  <si>
-    <t>债，奇迹</t>
-  </si>
-  <si>
     <t>丛林</t>
   </si>
   <si>
@@ -602,15 +529,6 @@
     <t>荒原</t>
   </si>
   <si>
-    <t>熵，谜</t>
-  </si>
-  <si>
-    <t>谜，幻觉</t>
-  </si>
-  <si>
-    <t>公元前7000</t>
-  </si>
-  <si>
     <t>群岛</t>
   </si>
   <si>
@@ -620,110 +538,92 @@
     <t>沼泽</t>
   </si>
   <si>
-    <t>遥远</t>
-  </si>
-  <si>
-    <t>周围</t>
-  </si>
-  <si>
-    <t>内部</t>
-  </si>
-  <si>
-    <t>热带</t>
-  </si>
-  <si>
-    <t>温带</t>
-  </si>
-  <si>
-    <t>寒带</t>
-  </si>
-  <si>
     <t>Hui</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>LiXing</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Cigarette</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>XingFu</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>TongKu</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>YiWang</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Zui</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>DongTu</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ZhanZheng</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ShaMo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Mi</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>BianZhengFa</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FanZao</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Literature</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Philosophy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Sociology</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Work</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Diploma</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Alcohol</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Icetea</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>YiWang,YiWang,TongKu,XingFu</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>LiXing,Hui</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
@@ -760,230 +660,365 @@
   <si>
     <t>你的大学文凭，全世界最没用的东西
 你学的是什么？</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Hai</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>PingYuan</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Shan</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>QunDao</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CongLin</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>HuangYuan</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ZhaoZe</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>幻觉</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>复仇</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>熵</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>律法</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>奇迹</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>债</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>帝国</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>冬</t>
   </si>
   <si>
     <t>革命</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>机器</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>疯狂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>HuanJue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Chat</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Zhai</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FengKuang</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FuChou</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>QiJi</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>DiGuo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Shang</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>LvFa</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>GeMing</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>JiQi</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>泡在水里</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小雨</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>干旱</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>火</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Huo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>谜，火</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>世界上唯一的万能药。
 意志力+3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>我们必须想象西西弗斯是幸福的。
 意志力-2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。
 意志力+5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>为短片攥写剧本,  一份勉强能糊口的编剧工作，自然也谈不上什么文学追求。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequiredCard</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>NewDistrict</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Oak Rd</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Downtown</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>WestHill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Guang</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>光</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RefreshChoice</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaximumUse</t>
   </si>
   <si>
     <t>BianZhengFa,Mi</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>DongTu,Zui</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ShaMo,ZhanZheng</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Recall what you have learned</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
+显然这对找到一份工作没有什么帮助。
+(今天已经回忆过了)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。
+显然这对找到一份工作没有什么帮助。
+(今天已经回忆过了)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。
+显然这对找到一份工作没有什么帮助。
+(今天已经回忆过了)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abyss Club</t>
+  </si>
+  <si>
+    <t>Edditor‘s Office</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardIndex</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Progress</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>choices</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardAdded</t>
+  </si>
+  <si>
+    <t>CardRemoved</t>
+  </si>
+  <si>
+    <t>DeltaWillPower</t>
+  </si>
+  <si>
+    <t>DeltaMoney</t>
+  </si>
+  <si>
+    <t>Targetprogress</t>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brad</t>
+  </si>
+  <si>
+    <t>Lawyer</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Editor</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brad Pitt</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lawyer Gin</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your Editor</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc4</t>
+  </si>
+  <si>
+    <t>cc5</t>
+  </si>
+  <si>
+    <t>cc6</t>
+  </si>
+  <si>
+    <t>cc7</t>
+  </si>
+  <si>
+    <t>cc8</t>
+  </si>
+  <si>
+    <t>cc9</t>
+  </si>
+  <si>
+    <t>cc10</t>
+  </si>
+  <si>
+    <t>cc11</t>
+  </si>
+  <si>
+    <t>cc12</t>
+  </si>
+  <si>
+    <t>cc13</t>
+  </si>
+  <si>
+    <t>cc14</t>
+  </si>
+  <si>
+    <t>Kid</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kids in Park</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bartender</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1094,8 +1129,23 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1147,8 +1197,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1186,27 +1242,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1214,101 +1278,127 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1528,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1568,308 +1658,255 @@
         <v>7</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="25" t="b">
-        <v>1</v>
-      </c>
+      <c r="A2" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="45"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="11">
-        <v>-2</v>
-      </c>
+      <c r="A3" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
-      <c r="I3" s="11" t="b">
-        <v>1</v>
-      </c>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2</v>
-      </c>
+      <c r="A4" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="42.75">
-      <c r="A5" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="25" t="b">
-        <v>1</v>
-      </c>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="25" t="b">
-        <v>1</v>
-      </c>
+      <c r="A6" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" ht="42.75">
       <c r="A8" s="24" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>214</v>
+        <v>8</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>189</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>43</v>
+      <c r="H8" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="I8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="24" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>44</v>
-      </c>
+      <c r="H9" s="38"/>
       <c r="I9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="24" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>217</v>
+        <v>8</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
       <c r="G10" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>46</v>
+      <c r="H10" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="I10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>125</v>
+        <v>172</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="29"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>126</v>
+      <c r="H11" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="I11" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="N11" s="16" t="s">
-        <v>269</v>
+      <c r="J11" s="25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="24" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="25" t="s">
-        <v>135</v>
+      <c r="H12" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="I12" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="24" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
@@ -1877,90 +1914,110 @@
         <v>1</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="I13" s="25" t="b">
         <v>1</v>
       </c>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="32">
+      <c r="A14" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I16" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="32">
         <v>-1</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5">
-      <c r="A15" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A16" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="32">
-        <v>3</v>
-      </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A17" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="E17" s="32">
-        <v>-2</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -1969,469 +2026,108 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="57">
-      <c r="A18" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>49</v>
+    <row r="18" spans="1:9" ht="16.5">
+      <c r="A18" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>207</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="E18" s="32">
+        <v>10</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A19" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="32">
+        <v>3</v>
+      </c>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A20" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E20" s="32">
+        <v>-2</v>
+      </c>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="57">
+      <c r="A21" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E21" s="32">
         <v>5</v>
       </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16.5">
-      <c r="A30" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16.5">
-      <c r="A31" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16.5">
-      <c r="A34" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="16.5">
-      <c r="A35" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16.5">
-      <c r="A36" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I36" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="16.5">
-      <c r="A37" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16.5">
-      <c r="A38" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I38" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16.5">
-      <c r="A39" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="16.5">
-      <c r="A40" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I40" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B41" t="s">
-        <v>236</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11" t="b">
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="17" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D43" s="21"/>
-      <c r="E43" s="12"/>
+      <c r="E43" s="11"/>
       <c r="F43" s="11" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
@@ -2440,199 +2136,664 @@
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>254</v>
+      <c r="A44" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="C44" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="21"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="21"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="16.5">
+      <c r="A54" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="16.5">
+      <c r="A55" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="11" t="s">
+      <c r="I55" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" s="12"/>
+      <c r="F56" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="16.5">
+      <c r="A58" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="12"/>
-      <c r="F45" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11" t="b">
+      <c r="I58" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="16.5">
+      <c r="A59" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="16.5">
+      <c r="A60" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="16.5">
+      <c r="A61" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="16.5">
+      <c r="A62" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="16.5">
+      <c r="A63" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="16.5">
+      <c r="A64" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" t="s">
+        <v>204</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="21"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="12"/>
+      <c r="F69" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3408FBE-15D1-42A9-9BFC-EC3E7DE1593E}">
-  <dimension ref="A1:J6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="2" width="14.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="J1" s="20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5">
-      <c r="A2" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20">
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20">
-        <v>1871</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20">
-        <v>3027</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="B1" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2646,7 +2807,7 @@
     <col min="2" max="2" width="19.625" customWidth="1"/>
     <col min="3" max="3" width="23.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="23.125" customWidth="1"/>
     <col min="8" max="8" width="16.125" customWidth="1"/>
@@ -2660,48 +2821,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="K1" s="13" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11" t="b">
@@ -2717,19 +2878,19 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" s="11" t="b">
         <v>0</v>
@@ -2744,13 +2905,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -2767,10 +2928,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -2786,16 +2947,18 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="128.25">
       <c r="A6" s="11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="11"/>
+        <v>64</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>238</v>
+      </c>
       <c r="D6" s="17" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2809,16 +2972,18 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" ht="114">
       <c r="A7" s="11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="11"/>
+        <v>66</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>239</v>
+      </c>
       <c r="D7" s="17" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2832,16 +2997,18 @@
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" ht="114">
       <c r="A8" s="11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>240</v>
+      </c>
       <c r="D8" s="17" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2857,10 +3024,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="C9" s="12"/>
       <c r="F9" s="11" t="b">
@@ -2870,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="I9" s="12">
         <v>1</v>
@@ -2880,10 +3047,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="C10" s="12"/>
       <c r="F10" s="11" t="b">
@@ -2893,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -2903,10 +3070,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="C11" s="12"/>
       <c r="F11" s="11" t="b">
@@ -2916,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="I11" s="12">
         <v>1</v>
@@ -2926,7 +3093,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2940,7 +3107,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2955,7 +3122,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2970,7 +3137,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -2985,7 +3152,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -3000,10 +3167,10 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="11" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3015,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -3025,10 +3192,10 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="12" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3046,14 +3213,14 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="11" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="17" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -3078,14 +3245,14 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="11" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="17" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="b">
@@ -3187,89 +3354,260 @@
       <c r="K26" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BEFD67-833C-4C4B-AEEA-212EA8D4541D}">
-  <dimension ref="A1:F1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3408FBE-15D1-42A9-9BFC-EC3E7DE1593E}">
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="5" width="19.5" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="27.125" customWidth="1"/>
+    <col min="5" max="5" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>55</v>
-      </c>
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5">
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCFD68A2-90ED-4996-BD29-B83331604818}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="16"/>
+    <col min="2" max="2" width="15.25" style="16" customWidth="1"/>
+    <col min="3" max="3" width="14.375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="16" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="16" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15">
+      <c r="A1" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="16" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="16" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="16" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="16" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -3286,22 +3624,22 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="6"/>
@@ -3318,22 +3656,22 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -3350,22 +3688,22 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -3382,22 +3720,22 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="16" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3641,12 +3979,12 @@
       <c r="R18" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
@@ -3654,12 +3992,12 @@
     <row r="1" spans="1:13">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3750,33 +4088,33 @@
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3784,47 +4122,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3832,26 +4170,26 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF9A1A-285A-4BA7-8832-B2D0F52F1F9B}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3863,266 +4201,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>146</v>
-      </c>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>163</v>
-      </c>
+      <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>165</v>
-      </c>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>164</v>
-      </c>
+      <c r="D5" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="2" width="14.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305D32EE-2FEF-4594-8BA7-4D35B119F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B41A96-543C-4BFE-BD5A-4ABA534D9E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="278">
   <si>
     <t>Index</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>Cinema</t>
-  </si>
-  <si>
-    <t>Gallery</t>
   </si>
   <si>
     <t>Home</t>
@@ -999,8 +996,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Bartender</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>Reusable</t>
+  </si>
+  <si>
+    <t>Shipyard</t>
   </si>
 </sst>
 </file>
@@ -1658,24 +1657,24 @@
         <v>7</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D2" s="45"/>
       <c r="E2" s="43"/>
@@ -1686,13 +1685,13 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3" s="21"/>
       <c r="E3" s="11"/>
@@ -1703,13 +1702,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="11"/>
@@ -1720,13 +1719,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>276</v>
-      </c>
       <c r="C5" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="11"/>
@@ -1736,15 +1735,9 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>254</v>
-      </c>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -1765,7 +1758,7 @@
     </row>
     <row r="8" spans="1:14" ht="42.75">
       <c r="A8" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>12</v>
@@ -1774,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
@@ -1790,7 +1783,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>14</v>
@@ -1799,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
@@ -1813,7 +1806,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>16</v>
@@ -1822,7 +1815,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
@@ -1841,7 +1834,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>17</v>
@@ -1850,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
@@ -1869,7 +1862,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>18</v>
@@ -1878,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
@@ -1897,7 +1890,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>37</v>
@@ -1906,7 +1899,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
@@ -1923,16 +1916,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="25"/>
@@ -1940,27 +1933,27 @@
         <v>1</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I14" s="25" t="b">
         <v>1</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
@@ -1968,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I15" s="25" t="b">
         <v>1</v>
@@ -1982,16 +1975,16 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="25"/>
@@ -1999,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I16" s="25" t="b">
         <v>1</v>
@@ -2007,7 +2000,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>19</v>
@@ -2028,10 +2021,10 @@
     </row>
     <row r="18" spans="1:9" ht="16.5">
       <c r="A18" s="34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>10</v>
@@ -2047,7 +2040,7 @@
     </row>
     <row r="19" spans="1:9" ht="29.25" customHeight="1">
       <c r="A19" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>39</v>
@@ -2056,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E19" s="32">
         <v>3</v>
@@ -2070,7 +2063,7 @@
     </row>
     <row r="20" spans="1:9" ht="29.25" customHeight="1">
       <c r="A20" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>40</v>
@@ -2079,7 +2072,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E20" s="32">
         <v>-2</v>
@@ -2093,7 +2086,7 @@
     </row>
     <row r="21" spans="1:9" ht="57">
       <c r="A21" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>41</v>
@@ -2102,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E21" s="32">
         <v>5</v>
@@ -2116,7 +2109,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>76</v>
@@ -2137,10 +2130,10 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>22</v>
@@ -2158,10 +2151,10 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>22</v>
@@ -2175,10 +2168,10 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>22</v>
@@ -2192,7 +2185,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>31</v>
@@ -2215,10 +2208,10 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>22</v>
@@ -2232,10 +2225,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>22</v>
@@ -2249,10 +2242,10 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>22</v>
@@ -2266,10 +2259,10 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>22</v>
@@ -2283,10 +2276,10 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>22</v>
@@ -2300,7 +2293,7 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>27</v>
@@ -2321,10 +2314,10 @@
     </row>
     <row r="54" spans="1:9" ht="16.5">
       <c r="A54" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>10</v>
@@ -2335,10 +2328,10 @@
     </row>
     <row r="55" spans="1:9" ht="16.5">
       <c r="A55" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>22</v>
@@ -2352,7 +2345,7 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>21</v>
@@ -2361,7 +2354,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="11" t="s">
@@ -2375,18 +2368,18 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B57" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="16.5">
       <c r="A58" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>22</v>
@@ -2400,10 +2393,10 @@
     </row>
     <row r="59" spans="1:9" ht="16.5">
       <c r="A59" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>22</v>
@@ -2417,10 +2410,10 @@
     </row>
     <row r="60" spans="1:9" ht="16.5">
       <c r="A60" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>22</v>
@@ -2434,10 +2427,10 @@
     </row>
     <row r="61" spans="1:9" ht="16.5">
       <c r="A61" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>22</v>
@@ -2451,10 +2444,10 @@
     </row>
     <row r="62" spans="1:9" ht="16.5">
       <c r="A62" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>22</v>
@@ -2468,10 +2461,10 @@
     </row>
     <row r="63" spans="1:9" ht="16.5">
       <c r="A63" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>22</v>
@@ -2485,10 +2478,10 @@
     </row>
     <row r="64" spans="1:9" ht="16.5">
       <c r="A64" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>22</v>
@@ -2502,10 +2495,10 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B65" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>22</v>
@@ -2519,7 +2512,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>25</v>
@@ -2542,7 +2535,7 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>29</v>
@@ -2563,10 +2556,10 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>22</v>
@@ -2580,7 +2573,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>33</v>
@@ -2626,31 +2619,31 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>85</v>
@@ -2658,47 +2651,47 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>87</v>
@@ -2706,47 +2699,47 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>86</v>
@@ -2754,42 +2747,42 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>94</v>
+        <v>112</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2955,10 +2948,10 @@
         <v>64</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2980,10 +2973,10 @@
         <v>66</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -3005,10 +2998,10 @@
         <v>68</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -3027,7 +3020,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C9" s="12"/>
       <c r="F9" s="11" t="b">
@@ -3037,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I9" s="12">
         <v>1</v>
@@ -3050,7 +3043,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C10" s="12"/>
       <c r="F10" s="11" t="b">
@@ -3060,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I10" s="12">
         <v>1</v>
@@ -3073,7 +3066,7 @@
         <v>36</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C11" s="12"/>
       <c r="F11" s="11" t="b">
@@ -3083,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I11" s="12">
         <v>1</v>
@@ -3182,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -3192,10 +3185,10 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3213,14 +3206,14 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -3245,14 +3238,14 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="b">
@@ -3372,19 +3365,19 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="C1" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="E1" s="48" t="s">
         <v>245</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>246</v>
       </c>
       <c r="J1" s="20"/>
     </row>
@@ -3456,7 +3449,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCFD68A2-90ED-4996-BD29-B83331604818}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="16"/>
@@ -3469,97 +3462,100 @@
     <col min="8" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:8" ht="15">
       <c r="A1" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D1" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="G1" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="G1" s="42" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="16" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="16" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="16" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="16" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="16" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="16" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="16" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="16" t="s">
+    <row r="8" spans="1:8">
+      <c r="A8" s="16" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="16" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="16" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="16" t="s">
+    <row r="10" spans="1:8">
+      <c r="A10" s="16" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="16" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" s="16" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="16" t="s">
+    <row r="12" spans="1:8">
+      <c r="A12" s="16" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="16" t="s">
+    <row r="13" spans="1:8">
+      <c r="A13" s="16" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="16" t="s">
+    <row r="14" spans="1:8">
+      <c r="A14" s="16" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="16" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" s="16" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="16" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3578,16 +3574,16 @@
         <v>75</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>138</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3607,7 +3603,7 @@
         <v>76</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -3630,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>27</v>
@@ -3665,13 +3661,13 @@
         <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -3688,7 +3684,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>76</v>
@@ -3697,10 +3693,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>19</v>
@@ -3720,22 +3716,22 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -4201,24 +4197,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>132</v>
-      </c>
       <c r="C1" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>134</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4227,10 +4223,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -4239,10 +4235,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -4251,10 +4247,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>4</v>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B41A96-543C-4BFE-BD5A-4ABA534D9E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E3D283-5A63-4360-B723-D9A6AF7DE103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="826" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="299">
   <si>
     <t>Index</t>
   </si>
@@ -430,63 +430,63 @@
   </si>
   <si>
     <t>CanBeDropped</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Index</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>dm1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MoneyReward</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RequiredCards</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>f29</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>f12</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>f13</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>f30</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>辩证法</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>谜</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>理性</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>灰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>痛苦</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>dm2</t>
@@ -499,19 +499,19 @@
   </si>
   <si>
     <t>理性灰</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>冻土沙漠</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>辩证法理性</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>理性沙漠</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>山</t>
@@ -536,91 +536,91 @@
   </si>
   <si>
     <t>Hui</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>LiXing</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Cigarette</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>XingFu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TongKu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>YiWang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Zui</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DongTu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ZhanZheng</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ShaMo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Mi</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BianZhengFa</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>FanZao</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Literature</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Philosophy</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Sociology</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Work</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Diploma</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Alcohol</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Icetea</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>YiWang,YiWang,TongKu,XingFu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>LiXing,Hui</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
@@ -657,248 +657,248 @@
   <si>
     <t>你的大学文凭，全世界最没用的东西
 你学的是什么？</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Hai</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PingYuan</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Shan</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>QunDao</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CongLin</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HuangYuan</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ZhaoZe</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>幻觉</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>复仇</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>熵</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>律法</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>奇迹</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>债</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>帝国</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>冬</t>
   </si>
   <si>
     <t>革命</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>机器</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>疯狂</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HuanJue</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chat</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Zhai</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>FengKuang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>FuChou</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>QiJi</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DiGuo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Shang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>LvFa</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>GeMing</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>JiQi</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>火</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Huo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>世界上唯一的万能药。
 意志力+3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>我们必须想象西西弗斯是幸福的。
 意志力-2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。
 意志力+5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>为短片攥写剧本,  一份勉强能糊口的编剧工作，自然也谈不上什么文学追求。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>NewDistrict</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Oak Rd</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Downtown</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>WestHill</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Guang</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>光</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RefreshChoice</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MaximumUse</t>
   </si>
   <si>
     <t>BianZhengFa,Mi</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DongTu,Zui</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ShaMo,ZhanZheng</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Recall what you have learned</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
 显然这对找到一份工作没有什么帮助。
 (今天已经回忆过了)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。
 显然这对找到一份工作没有什么帮助。
 (今天已经回忆过了)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。
 显然这对找到一份工作没有什么帮助。
 (今天已经回忆过了)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Abyss Club</t>
   </si>
   <si>
     <t>Edditor‘s Office</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Node</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CardIndex</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Progress</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>choices</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Text</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Text</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CardAdded</t>
@@ -917,42 +917,42 @@
   </si>
   <si>
     <t>Character</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Brad</t>
   </si>
   <si>
     <t>Lawyer</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Editor</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Brad Pitt</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Lawyer Gin</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Your Editor</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cc1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cc2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cc3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cc4</t>
@@ -989,35 +989,112 @@
   </si>
   <si>
     <t>Kid</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Kids in Park</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Reusable</t>
   </si>
   <si>
     <t>Shipyard</t>
+  </si>
+  <si>
+    <t>progress0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>progress1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>progress2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>progress3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>m2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>m4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>progress4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc10</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>reuse</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc3,cc4,cc11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc5,cc6,cc11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc7,cc8,cc11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc9,cc10,cc11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cc1,cc2,cc11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1109,11 +1186,15 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1265,11 +1346,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1277,127 +1361,126 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1617,18 +1700,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N69"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="37.125" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" customWidth="1"/>
+    <col min="4" max="4" width="37.08203125" customWidth="1"/>
     <col min="5" max="5" width="7.75" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1">
@@ -1717,7 +1800,7 @@
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" ht="13" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>274</v>
       </c>
@@ -1734,88 +1817,122 @@
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+    <row r="6" spans="1:14" ht="42">
+      <c r="A6" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" ht="42.75">
+      <c r="A7" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>188</v>
+      <c r="D8" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="25" t="s">
-        <v>13</v>
+      <c r="H8" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="I8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="I9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
@@ -1823,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I10" s="25" t="b">
         <v>1</v>
@@ -1834,72 +1951,70 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="24" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>181</v>
+      <c r="D11" s="27" t="s">
+        <v>184</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>35</v>
+      <c r="H11" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="I11" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="25" t="b">
-        <v>1</v>
-      </c>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>18</v>
+        <v>208</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>114</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="25"/>
+      <c r="D12" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="29"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>36</v>
+      <c r="H12" s="25" t="s">
+        <v>115</v>
       </c>
       <c r="I12" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="25" t="b">
-        <v>1</v>
+      <c r="N12" s="16" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="24" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>184</v>
+      <c r="D13" s="26" t="s">
+        <v>186</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
@@ -1907,110 +2022,98 @@
         <v>1</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="I13" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>114</v>
+        <v>177</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="E14" s="29"/>
+      <c r="D14" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="25"/>
       <c r="F14" s="25"/>
       <c r="G14" s="25" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I14" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="N14" s="16" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="I15" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="A15" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="32">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="14.5">
+      <c r="A16" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="29.25" customHeight="1">
       <c r="A17" s="31" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="37"/>
+      <c r="D17" s="33" t="s">
+        <v>220</v>
+      </c>
       <c r="E17" s="32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -2019,40 +2122,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5">
-      <c r="A18" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>206</v>
+    <row r="18" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A18" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>40</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
+      <c r="D18" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E18" s="32">
+        <v>-2</v>
+      </c>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
       <c r="I18" s="32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="29.25" customHeight="1">
+    <row r="19" spans="1:9" ht="56">
       <c r="A19" s="31" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" s="32" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E19" s="32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -2061,64 +2168,423 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A20" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="32" t="s">
+    <row r="20" spans="1:9">
+      <c r="A20" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="21"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="21"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14.5">
+      <c r="A31" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="E20" s="32">
-        <v>-2</v>
-      </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="57">
-      <c r="A21" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E21" s="32">
-        <v>5</v>
-      </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32" t="b">
+      <c r="I31" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="14.5">
+      <c r="A32" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="14.5">
+      <c r="A35" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.5">
+      <c r="A36" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.5">
+      <c r="A37" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14.5">
+      <c r="A38" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14.5">
+      <c r="A39" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="14.5">
+      <c r="A40" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="14.5">
+      <c r="A41" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="17" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="11"/>
+      <c r="D43" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="12"/>
       <c r="F43" s="11" t="s">
         <v>23</v>
       </c>
@@ -2130,18 +2596,18 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D44" s="21"/>
-      <c r="E44" s="11"/>
+      <c r="E44" s="12"/>
       <c r="F44" s="11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11"/>
@@ -2151,451 +2617,46 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>157</v>
+        <v>219</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I45" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>154</v>
+      <c r="A46" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>22</v>
       </c>
+      <c r="D46" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="12"/>
       <c r="F46" s="11" t="s">
-        <v>28</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="16.5">
-      <c r="A54" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I54" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="16.5">
-      <c r="A55" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B55" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="16.5">
-      <c r="A58" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="B58" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="16.5">
-      <c r="A59" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B59" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="16.5">
-      <c r="A60" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B60" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I60" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="16.5">
-      <c r="A61" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B61" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I61" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="16.5">
-      <c r="A62" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B62" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="16.5">
-      <c r="A63" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="B63" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I63" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="16.5">
-      <c r="A64" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B65" t="s">
-        <v>203</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I65" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="21"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2604,9 +2665,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="14.875" customWidth="1"/>
+    <col min="1" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2786,7 +2847,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2794,18 +2855,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
+    <col min="2" max="2" width="19.58203125" customWidth="1"/>
     <col min="3" max="3" width="23.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="15.08203125" customWidth="1"/>
     <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="23.125" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="6" max="6" width="17.58203125" customWidth="1"/>
+    <col min="7" max="7" width="23.08203125" customWidth="1"/>
+    <col min="8" max="8" width="16.08203125" customWidth="1"/>
     <col min="9" max="9" width="15.5" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="10.58203125" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2940,7 +3001,7 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
     </row>
-    <row r="6" spans="1:11" ht="128.25">
+    <row r="6" spans="1:11" ht="126">
       <c r="A6" s="11" t="s">
         <v>63</v>
       </c>
@@ -2965,7 +3026,7 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
     </row>
-    <row r="7" spans="1:11" ht="114">
+    <row r="7" spans="1:11" ht="112">
       <c r="A7" s="11" t="s">
         <v>65</v>
       </c>
@@ -2990,7 +3051,7 @@
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
     </row>
-    <row r="8" spans="1:11" ht="114">
+    <row r="8" spans="1:11" ht="112">
       <c r="A8" s="11" t="s">
         <v>67</v>
       </c>
@@ -3347,7 +3408,7 @@
       <c r="K26" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3355,15 +3416,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3408FBE-15D1-42A9-9BFC-EC3E7DE1593E}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="27.125" customWidth="1"/>
+    <col min="3" max="3" width="27.08203125" customWidth="1"/>
     <col min="5" max="5" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10" ht="14.5">
       <c r="A1" s="42" t="s">
         <v>243</v>
       </c>
@@ -3376,17 +3437,27 @@
       <c r="D1" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="47" t="s">
         <v>245</v>
       </c>
       <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:10" ht="16.5">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
+    <row r="2" spans="1:10" ht="14.5">
+      <c r="A2" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="46">
+        <v>0</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>298</v>
+      </c>
       <c r="F2" s="19"/>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -3394,11 +3465,21 @@
       <c r="J2" s="20"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="19"/>
+      <c r="A3" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="20">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>294</v>
+      </c>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
@@ -3406,11 +3487,21 @@
       <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="19"/>
+      <c r="A4" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="20">
+        <v>2</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>295</v>
+      </c>
       <c r="F4" s="19"/>
       <c r="G4" s="20"/>
       <c r="H4" s="20"/>
@@ -3418,11 +3509,21 @@
       <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="19"/>
+      <c r="A5" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="20">
+        <v>3</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>296</v>
+      </c>
       <c r="F5" s="19"/>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
@@ -3430,11 +3531,21 @@
       <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
+      <c r="A6" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="20">
+        <v>4</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>297</v>
+      </c>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
@@ -3442,7 +3553,7 @@
       <c r="J6" s="19"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3450,19 +3561,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCFD68A2-90ED-4996-BD29-B83331604818}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="16"/>
     <col min="2" max="2" width="15.25" style="16" customWidth="1"/>
-    <col min="3" max="3" width="14.375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="15.08203125" style="16" customWidth="1"/>
     <col min="8" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" ht="14.5">
       <c r="A1" s="40" t="s">
         <v>130</v>
       </c>
@@ -3492,56 +3603,125 @@
       <c r="A2" s="16" t="s">
         <v>260</v>
       </c>
+      <c r="B2" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" s="16">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="16">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="16" t="s">
         <v>261</v>
       </c>
+      <c r="B3" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="16">
+        <v>2</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="16">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="16" t="s">
         <v>262</v>
       </c>
+      <c r="B4" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="16">
+        <v>4</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="16" t="s">
         <v>263</v>
       </c>
+      <c r="B5" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5" s="16">
+        <v>3</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="16" t="s">
         <v>264</v>
       </c>
+      <c r="B6" s="16" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="16" t="s">
         <v>265</v>
       </c>
+      <c r="B7" s="16" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
         <v>266</v>
       </c>
+      <c r="B8" s="16" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="16" t="s">
         <v>267</v>
       </c>
+      <c r="B9" s="16" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="16" t="s">
         <v>268</v>
       </c>
+      <c r="B10" s="16" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
         <v>269</v>
       </c>
+      <c r="B11" s="16" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="16" t="s">
         <v>270</v>
       </c>
+      <c r="B12" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G12" s="16">
+        <v>5</v>
+      </c>
+      <c r="H12" s="16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="16" t="s">
@@ -3559,7 +3739,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3567,7 +3747,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="5.58203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="B1" s="2" t="s">
@@ -3975,7 +4155,7 @@
       <c r="R18" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3983,7 +4163,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="5.58203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3"/>
@@ -4084,7 +4264,7 @@
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4092,7 +4272,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="5.58203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
@@ -4132,7 +4312,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4140,7 +4320,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="5.58203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="2" t="s">
@@ -4180,7 +4360,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4188,9 +4368,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF9A1A-285A-4BA7-8832-B2D0F52F1F9B}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
@@ -4258,7 +4438,7 @@
       <c r="D5" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>